--- a/Resumo_Atividades_Qualidade_2026.xlsx
+++ b/Resumo_Atividades_Qualidade_2026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1218"/>
+  <dimension ref="A1:G1231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30511,28 +30511,28 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B971" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="C971" s="2" t="n">
-        <v>46029.34027777778</v>
+        <v>46128.40277777778</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
-          <t>PPG-WS</t>
+          <t>RDO-09</t>
         </is>
       </c>
       <c r="E971" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G971" t="n">
@@ -30542,28 +30542,28 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B972" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="C972" s="2" t="n">
-        <v>46029.34583333333</v>
+        <v>46128.40416666667</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>PPG-WS</t>
+          <t>RDO-09</t>
         </is>
       </c>
       <c r="E972" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G972" t="n">
@@ -30573,28 +30573,28 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B973" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="C973" s="2" t="n">
-        <v>46029.35416666666</v>
+        <v>46128.40555555555</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
-          <t>PPG-00</t>
+          <t>RDO-09</t>
         </is>
       </c>
       <c r="E973" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G973" t="n">
@@ -30604,28 +30604,28 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B974" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="C974" s="2" t="n">
-        <v>46029.35416666666</v>
+        <v>46128.40694444445</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>PPG-01</t>
+          <t>RDO-09</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G974" t="n">
@@ -30635,28 +30635,28 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B975" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="C975" s="2" t="n">
-        <v>46029.35416666666</v>
+        <v>46128.44652777778</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
-          <t>PPG-02</t>
+          <t>RDO-09</t>
         </is>
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>APR - PT</t>
         </is>
       </c>
       <c r="G975" t="n">
@@ -30666,28 +30666,28 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BJS</t>
         </is>
       </c>
       <c r="B976" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="C976" s="2" t="n">
-        <v>46029.35416666666</v>
+        <v>46128.44652777778</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>PPG-10</t>
+          <t>RDO-09</t>
         </is>
       </c>
       <c r="E976" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G976" t="n">
@@ -30704,11 +30704,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C977" s="2" t="n">
-        <v>46029.35416666666</v>
+        <v>46029.34027777778</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>PPG-14</t>
+          <t>PPG-WS</t>
         </is>
       </c>
       <c r="E977" t="inlineStr">
@@ -30735,11 +30735,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C978" s="2" t="n">
-        <v>46029.35416666666</v>
+        <v>46029.34583333333</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
-          <t>PPG-17</t>
+          <t>PPG-WS</t>
         </is>
       </c>
       <c r="E978" t="inlineStr">
@@ -30770,7 +30770,7 @@
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>PPG-29</t>
+          <t>PPG-00</t>
         </is>
       </c>
       <c r="E979" t="inlineStr">
@@ -30801,7 +30801,7 @@
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>PPG-2K</t>
+          <t>PPG-01</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
@@ -30832,7 +30832,7 @@
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>PPG-30</t>
+          <t>PPG-02</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>PPG-41</t>
+          <t>PPG-10</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>PPG-44</t>
+          <t>PPG-14</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
@@ -30925,7 +30925,7 @@
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>PPG-45</t>
+          <t>PPG-17</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>PPG-55</t>
+          <t>PPG-29</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -30987,7 +30987,7 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>PPG-5D</t>
+          <t>PPG-2K</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -31018,7 +31018,7 @@
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>PPG-63</t>
+          <t>PPG-30</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>PPG-6C</t>
+          <t>PPG-41</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
@@ -31080,7 +31080,7 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>PPG-78</t>
+          <t>PPG-44</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
@@ -31111,7 +31111,7 @@
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>PPG-7C</t>
+          <t>PPG-45</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
@@ -31142,7 +31142,7 @@
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>PPG-89</t>
+          <t>PPG-55</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
@@ -31173,7 +31173,7 @@
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>PPG-91</t>
+          <t>PPG-5D</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>PPG-97</t>
+          <t>PPG-63</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
@@ -31231,11 +31231,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C994" s="2" t="n">
-        <v>46029.36111111111</v>
+        <v>46029.35416666666</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>PPG-53</t>
+          <t>PPG-6C</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
@@ -31262,11 +31262,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C995" s="2" t="n">
-        <v>46029.36111111111</v>
+        <v>46029.35416666666</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>PPG-67</t>
+          <t>PPG-78</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
@@ -31293,11 +31293,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C996" s="2" t="n">
-        <v>46029.375</v>
+        <v>46029.35416666666</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>PPG-19</t>
+          <t>PPG-7C</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
@@ -31324,11 +31324,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C997" s="2" t="n">
-        <v>46029.39583333334</v>
+        <v>46029.35416666666</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>PPG-1K</t>
+          <t>PPG-89</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
@@ -31355,11 +31355,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C998" s="2" t="n">
-        <v>46029.41666666666</v>
+        <v>46029.35416666666</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>PPG-WS</t>
+          <t>PPG-91</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -31386,11 +31386,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C999" s="2" t="n">
-        <v>46030</v>
+        <v>46029.35416666666</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>PPG--1</t>
+          <t>PPG-97</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -31417,11 +31417,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1000" s="2" t="n">
-        <v>46030</v>
+        <v>46029.36111111111</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>PPG-11</t>
+          <t>PPG-53</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="G1000" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1001">
@@ -31448,11 +31448,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1001" s="2" t="n">
-        <v>46030</v>
+        <v>46029.36111111111</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>PPG-18</t>
+          <t>PPG-67</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
@@ -31479,11 +31479,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1002" s="2" t="n">
-        <v>46030</v>
+        <v>46029.375</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>PPG-27</t>
+          <t>PPG-19</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
@@ -31510,11 +31510,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1003" s="2" t="n">
-        <v>46030</v>
+        <v>46029.39583333334</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>PPG-30</t>
+          <t>PPG-1K</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
@@ -31541,11 +31541,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1004" s="2" t="n">
-        <v>46030</v>
+        <v>46029.41666666666</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>PPG-33</t>
+          <t>PPG-WS</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>PPG-34</t>
+          <t>PPG--1</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -31607,7 +31607,7 @@
       </c>
       <c r="D1006" t="inlineStr">
         <is>
-          <t>PPG-38</t>
+          <t>PPG-11</t>
         </is>
       </c>
       <c r="E1006" t="inlineStr">
@@ -31621,7 +31621,7 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1007">
@@ -31638,7 +31638,7 @@
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>PPG-41</t>
+          <t>PPG-18</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
@@ -31652,7 +31652,7 @@
         </is>
       </c>
       <c r="G1007" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1008">
@@ -31669,7 +31669,7 @@
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>PPG-53</t>
+          <t>PPG-27</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>PPG-56</t>
+          <t>PPG-30</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
@@ -31731,7 +31731,7 @@
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>PPG-57</t>
+          <t>PPG-33</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="D1011" t="inlineStr">
         <is>
-          <t>PPG-60</t>
+          <t>PPG-34</t>
         </is>
       </c>
       <c r="E1011" t="inlineStr">
@@ -31793,7 +31793,7 @@
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>PPG-61</t>
+          <t>PPG-38</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -31824,7 +31824,7 @@
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>PPG-67</t>
+          <t>PPG-41</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
@@ -31838,7 +31838,7 @@
         </is>
       </c>
       <c r="G1013" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1014">
@@ -31855,7 +31855,7 @@
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>PPG-74</t>
+          <t>PPG-53</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>PPG-84</t>
+          <t>PPG-56</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
@@ -31917,7 +31917,7 @@
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>PPG-85</t>
+          <t>PPG-57</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>PPG-86</t>
+          <t>PPG-60</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
@@ -31979,7 +31979,7 @@
       </c>
       <c r="D1018" t="inlineStr">
         <is>
-          <t>PPG-91</t>
+          <t>PPG-61</t>
         </is>
       </c>
       <c r="E1018" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>PPG-94</t>
+          <t>PPG-67</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -32041,7 +32041,7 @@
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>PPG-MV</t>
+          <t>PPG-74</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
@@ -32055,7 +32055,7 @@
         </is>
       </c>
       <c r="G1020" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1021">
@@ -32068,11 +32068,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1021" s="2" t="n">
-        <v>46030.33333333334</v>
+        <v>46030</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>PPG-43</t>
+          <t>PPG-84</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
@@ -32099,11 +32099,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1022" s="2" t="n">
-        <v>46030.33333333334</v>
+        <v>46030</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>PPG-88</t>
+          <t>PPG-85</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
@@ -32130,11 +32130,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1023" s="2" t="n">
-        <v>46030.375</v>
+        <v>46030</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
-          <t>PPG-06</t>
+          <t>PPG-86</t>
         </is>
       </c>
       <c r="E1023" t="inlineStr">
@@ -32161,11 +32161,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1024" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>PPG-02</t>
+          <t>PPG-91</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -32192,11 +32192,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1025" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
-          <t>PPG-08</t>
+          <t>PPG-94</t>
         </is>
       </c>
       <c r="E1025" t="inlineStr">
@@ -32223,11 +32223,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1026" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
-          <t>PPG-11</t>
+          <t>PPG-MV</t>
         </is>
       </c>
       <c r="E1026" t="inlineStr">
@@ -32241,7 +32241,7 @@
         </is>
       </c>
       <c r="G1026" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1027">
@@ -32254,11 +32254,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1027" s="2" t="n">
-        <v>46031</v>
+        <v>46030.33333333334</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>PPG-16</t>
+          <t>PPG-43</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
@@ -32285,11 +32285,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1028" s="2" t="n">
-        <v>46031</v>
+        <v>46030.33333333334</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
-          <t>PPG-30</t>
+          <t>PPG-88</t>
         </is>
       </c>
       <c r="E1028" t="inlineStr">
@@ -32316,11 +32316,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1029" s="2" t="n">
-        <v>46031</v>
+        <v>46030.375</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
-          <t>PPG-32</t>
+          <t>PPG-06</t>
         </is>
       </c>
       <c r="E1029" t="inlineStr">
@@ -32351,7 +32351,7 @@
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>PPG-33</t>
+          <t>PPG-02</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
@@ -32382,7 +32382,7 @@
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>PPG-54</t>
+          <t>PPG-08</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
@@ -32413,7 +32413,7 @@
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>PPG-68</t>
+          <t>PPG-11</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>PPG-74</t>
+          <t>PPG-16</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
@@ -32458,7 +32458,7 @@
         </is>
       </c>
       <c r="G1033" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1034">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>PPG-76</t>
+          <t>PPG-30</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>PPG-90</t>
+          <t>PPG-32</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>PPG-MV</t>
+          <t>PPG-33</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
@@ -32551,7 +32551,7 @@
         </is>
       </c>
       <c r="G1036" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1037">
@@ -32564,11 +32564,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1037" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>PPG--3</t>
+          <t>PPG-54</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
@@ -32595,11 +32595,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1038" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
-          <t>PPG--4</t>
+          <t>PPG-68</t>
         </is>
       </c>
       <c r="E1038" t="inlineStr">
@@ -32626,11 +32626,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1039" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
-          <t>PPG-00</t>
+          <t>PPG-74</t>
         </is>
       </c>
       <c r="E1039" t="inlineStr">
@@ -32644,7 +32644,7 @@
         </is>
       </c>
       <c r="G1039" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1040">
@@ -32657,11 +32657,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1040" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
-          <t>PPG-13</t>
+          <t>PPG-76</t>
         </is>
       </c>
       <c r="E1040" t="inlineStr">
@@ -32688,11 +32688,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1041" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>PPG-17</t>
+          <t>PPG-90</t>
         </is>
       </c>
       <c r="E1041" t="inlineStr">
@@ -32719,11 +32719,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1042" s="2" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
-          <t>PPG-29</t>
+          <t>PPG-MV</t>
         </is>
       </c>
       <c r="E1042" t="inlineStr">
@@ -32737,7 +32737,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1043">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="D1043" t="inlineStr">
         <is>
-          <t>PPG-31</t>
+          <t>PPG--3</t>
         </is>
       </c>
       <c r="E1043" t="inlineStr">
@@ -32785,7 +32785,7 @@
       </c>
       <c r="D1044" t="inlineStr">
         <is>
-          <t>PPG-33</t>
+          <t>PPG--4</t>
         </is>
       </c>
       <c r="E1044" t="inlineStr">
@@ -32799,7 +32799,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1045">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="D1045" t="inlineStr">
         <is>
-          <t>PPG-37</t>
+          <t>PPG-00</t>
         </is>
       </c>
       <c r="E1045" t="inlineStr">
@@ -32847,7 +32847,7 @@
       </c>
       <c r="D1046" t="inlineStr">
         <is>
-          <t>PPG-83</t>
+          <t>PPG-13</t>
         </is>
       </c>
       <c r="E1046" t="inlineStr">
@@ -32878,7 +32878,7 @@
       </c>
       <c r="D1047" t="inlineStr">
         <is>
-          <t>PPG-91</t>
+          <t>PPG-17</t>
         </is>
       </c>
       <c r="E1047" t="inlineStr">
@@ -32909,7 +32909,7 @@
       </c>
       <c r="D1048" t="inlineStr">
         <is>
-          <t>PPG-96</t>
+          <t>PPG-29</t>
         </is>
       </c>
       <c r="E1048" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="D1049" t="inlineStr">
         <is>
-          <t>PPG-MV</t>
+          <t>PPG-31</t>
         </is>
       </c>
       <c r="E1049" t="inlineStr">
@@ -32954,7 +32954,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1050">
@@ -32967,11 +32967,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1050" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
-          <t>PPG-02</t>
+          <t>PPG-33</t>
         </is>
       </c>
       <c r="E1050" t="inlineStr">
@@ -32985,7 +32985,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1051">
@@ -32998,11 +32998,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1051" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
-          <t>PPG-36</t>
+          <t>PPG-37</t>
         </is>
       </c>
       <c r="E1051" t="inlineStr">
@@ -33029,11 +33029,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1052" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>PPG-48</t>
+          <t>PPG-83</t>
         </is>
       </c>
       <c r="E1052" t="inlineStr">
@@ -33047,7 +33047,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1053">
@@ -33060,11 +33060,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1053" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
-          <t>PPG-53</t>
+          <t>PPG-91</t>
         </is>
       </c>
       <c r="E1053" t="inlineStr">
@@ -33091,11 +33091,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1054" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
-          <t>PPG-81</t>
+          <t>PPG-96</t>
         </is>
       </c>
       <c r="E1054" t="inlineStr">
@@ -33122,7 +33122,7 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1055" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1056">
@@ -33153,11 +33153,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1056" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
-          <t>PPG-18</t>
+          <t>PPG-02</t>
         </is>
       </c>
       <c r="E1056" t="inlineStr">
@@ -33184,11 +33184,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1057" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
-          <t>PPG-22</t>
+          <t>PPG-36</t>
         </is>
       </c>
       <c r="E1057" t="inlineStr">
@@ -33215,11 +33215,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1058" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
-          <t>PPG-43</t>
+          <t>PPG-48</t>
         </is>
       </c>
       <c r="E1058" t="inlineStr">
@@ -33233,7 +33233,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1059">
@@ -33246,11 +33246,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1059" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
-          <t>PPG-52</t>
+          <t>PPG-53</t>
         </is>
       </c>
       <c r="E1059" t="inlineStr">
@@ -33277,11 +33277,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1060" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>PPG-69</t>
+          <t>PPG-81</t>
         </is>
       </c>
       <c r="E1060" t="inlineStr">
@@ -33308,11 +33308,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1061" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>PPG-89</t>
+          <t>PPG-MV</t>
         </is>
       </c>
       <c r="E1061" t="inlineStr">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1062">
@@ -33343,7 +33343,7 @@
       </c>
       <c r="D1062" t="inlineStr">
         <is>
-          <t>PPG-MV</t>
+          <t>PPG-18</t>
         </is>
       </c>
       <c r="E1062" t="inlineStr">
@@ -33357,7 +33357,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1063">
@@ -33370,11 +33370,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1063" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
-          <t>PPG-00</t>
+          <t>PPG-22</t>
         </is>
       </c>
       <c r="E1063" t="inlineStr">
@@ -33388,7 +33388,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1064">
@@ -33401,11 +33401,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1064" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
-          <t>PPG-12</t>
+          <t>PPG-43</t>
         </is>
       </c>
       <c r="E1064" t="inlineStr">
@@ -33432,11 +33432,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1065" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
-          <t>PPG-21</t>
+          <t>PPG-52</t>
         </is>
       </c>
       <c r="E1065" t="inlineStr">
@@ -33463,11 +33463,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1066" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
-          <t>PPG-28</t>
+          <t>PPG-69</t>
         </is>
       </c>
       <c r="E1066" t="inlineStr">
@@ -33494,11 +33494,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1067" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>PPG-29</t>
+          <t>PPG-89</t>
         </is>
       </c>
       <c r="E1067" t="inlineStr">
@@ -33525,11 +33525,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1068" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
-          <t>PPG-45</t>
+          <t>PPG-MV</t>
         </is>
       </c>
       <c r="E1068" t="inlineStr">
@@ -33543,7 +33543,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1069">
@@ -33560,7 +33560,7 @@
       </c>
       <c r="D1069" t="inlineStr">
         <is>
-          <t>PPG-67</t>
+          <t>PPG-00</t>
         </is>
       </c>
       <c r="E1069" t="inlineStr">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1070">
@@ -33591,7 +33591,7 @@
       </c>
       <c r="D1070" t="inlineStr">
         <is>
-          <t>PPG-81</t>
+          <t>PPG-12</t>
         </is>
       </c>
       <c r="E1070" t="inlineStr">
@@ -33605,7 +33605,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1071">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t>PPG-93</t>
+          <t>PPG-21</t>
         </is>
       </c>
       <c r="E1071" t="inlineStr">
@@ -33653,7 +33653,7 @@
       </c>
       <c r="D1072" t="inlineStr">
         <is>
-          <t>PPG-96</t>
+          <t>PPG-28</t>
         </is>
       </c>
       <c r="E1072" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="D1073" t="inlineStr">
         <is>
-          <t>PPG-MV</t>
+          <t>PPG-29</t>
         </is>
       </c>
       <c r="E1073" t="inlineStr">
@@ -33698,7 +33698,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1074">
@@ -33715,7 +33715,7 @@
       </c>
       <c r="D1074" t="inlineStr">
         <is>
-          <t>PPG-WS</t>
+          <t>PPG-45</t>
         </is>
       </c>
       <c r="E1074" t="inlineStr">
@@ -33742,11 +33742,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1075" s="2" t="n">
-        <v>46038.70833333334</v>
+        <v>46037</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
-          <t>PPG-18</t>
+          <t>PPG-67</t>
         </is>
       </c>
       <c r="E1075" t="inlineStr">
@@ -33773,11 +33773,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1076" s="2" t="n">
-        <v>46038.70833333334</v>
+        <v>46037</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
-          <t>PPG-40</t>
+          <t>PPG-81</t>
         </is>
       </c>
       <c r="E1076" t="inlineStr">
@@ -33791,7 +33791,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1077">
@@ -33804,11 +33804,11 @@
         <v>46029.33333333334</v>
       </c>
       <c r="C1077" s="2" t="n">
-        <v>46076</v>
+        <v>46037</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
-          <t>PPG-14</t>
+          <t>PPG-93</t>
         </is>
       </c>
       <c r="E1077" t="inlineStr">
@@ -33832,14 +33832,14 @@
         </is>
       </c>
       <c r="B1078" s="2" t="n">
-        <v>46036.33333333334</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="C1078" s="2" t="n">
-        <v>46036.375</v>
+        <v>46037</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
-          <t>PPG-01</t>
+          <t>PPG-96</t>
         </is>
       </c>
       <c r="E1078" t="inlineStr">
@@ -33863,28 +33863,28 @@
         </is>
       </c>
       <c r="B1079" s="2" t="n">
-        <v>46058.54166666666</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="C1079" s="2" t="n">
-        <v>46058.70833333334</v>
+        <v>46037</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>PPG-MV</t>
         </is>
       </c>
       <c r="E1079" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1079" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1080">
@@ -33894,24 +33894,24 @@
         </is>
       </c>
       <c r="B1080" s="2" t="n">
-        <v>46058.58819444444</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="C1080" s="2" t="n">
-        <v>46058.70833333334</v>
+        <v>46037</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>PPG-WS</t>
         </is>
       </c>
       <c r="E1080" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO DE EQUIPE</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1080" t="n">
@@ -33925,24 +33925,24 @@
         </is>
       </c>
       <c r="B1081" s="2" t="n">
-        <v>46059.35416666666</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="C1081" s="2" t="n">
-        <v>46059.5</v>
+        <v>46038.70833333334</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
-          <t>MOR-19</t>
+          <t>PPG-18</t>
         </is>
       </c>
       <c r="E1081" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO DE EQUIPE</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1081" t="n">
@@ -33956,24 +33956,24 @@
         </is>
       </c>
       <c r="B1082" s="2" t="n">
-        <v>46059.375</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="C1082" s="2" t="n">
-        <v>46059.51736111111</v>
+        <v>46038.70833333334</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
-          <t>MOR-19</t>
+          <t>PPG-40</t>
         </is>
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1082" t="n">
@@ -33987,24 +33987,24 @@
         </is>
       </c>
       <c r="B1083" s="2" t="n">
-        <v>46059.54166666666</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="C1083" s="2" t="n">
-        <v>46059.64513888889</v>
+        <v>46076</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>PPG-14</t>
         </is>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1083" t="n">
@@ -34018,24 +34018,24 @@
         </is>
       </c>
       <c r="B1084" s="2" t="n">
-        <v>46059.56111111111</v>
+        <v>46036.33333333334</v>
       </c>
       <c r="C1084" s="2" t="n">
-        <v>46059.64444444444</v>
+        <v>46036.375</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>PPG-01</t>
         </is>
       </c>
       <c r="E1084" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
-          <t>AVALIAÇÃO DE EQUIPE</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1084" t="n">
@@ -34049,14 +34049,14 @@
         </is>
       </c>
       <c r="B1085" s="2" t="n">
-        <v>46065.58333333334</v>
+        <v>46058.54166666666</v>
       </c>
       <c r="C1085" s="2" t="n">
-        <v>46065.71875</v>
+        <v>46058.70833333334</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
-          <t>COQ-07</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1085" t="inlineStr">
@@ -34080,24 +34080,24 @@
         </is>
       </c>
       <c r="B1086" s="2" t="n">
-        <v>46073.33333333334</v>
+        <v>46058.58819444444</v>
       </c>
       <c r="C1086" s="2" t="n">
-        <v>46073.5</v>
+        <v>46058.70833333334</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
-          <t>CAJ-05</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>AVALIAÇÃO DE EQUIPE</t>
         </is>
       </c>
       <c r="G1086" t="n">
@@ -34111,24 +34111,24 @@
         </is>
       </c>
       <c r="B1087" s="2" t="n">
-        <v>46076.54166666666</v>
+        <v>46059.35416666666</v>
       </c>
       <c r="C1087" s="2" t="n">
-        <v>46076.69722222222</v>
+        <v>46059.5</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
-          <t>CAJ-13</t>
+          <t>MOR-19</t>
         </is>
       </c>
       <c r="E1087" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>AVALIAÇÃO DE EQUIPE</t>
         </is>
       </c>
       <c r="G1087" t="n">
@@ -34142,24 +34142,24 @@
         </is>
       </c>
       <c r="B1088" s="2" t="n">
-        <v>46076.66180555556</v>
+        <v>46059.375</v>
       </c>
       <c r="C1088" s="2" t="n">
-        <v>46076.70347222222</v>
+        <v>46059.51736111111</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
-          <t>PPG-86</t>
+          <t>MOR-19</t>
         </is>
       </c>
       <c r="E1088" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1088" t="n">
@@ -34173,24 +34173,24 @@
         </is>
       </c>
       <c r="B1089" s="2" t="n">
-        <v>46076.69444444445</v>
+        <v>46059.54166666666</v>
       </c>
       <c r="C1089" s="2" t="n">
-        <v>46076.70416666667</v>
+        <v>46059.64513888889</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
-          <t>PPG-12</t>
+          <t>MOR-18</t>
         </is>
       </c>
       <c r="E1089" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1089" t="n">
@@ -34204,24 +34204,24 @@
         </is>
       </c>
       <c r="B1090" s="2" t="n">
-        <v>46079.375</v>
+        <v>46059.56111111111</v>
       </c>
       <c r="C1090" s="2" t="n">
-        <v>46079.5</v>
+        <v>46059.64444444444</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
-          <t>BUR-01</t>
+          <t>MOR-18</t>
         </is>
       </c>
       <c r="E1090" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>AVALIAÇÃO DE EQUIPE</t>
         </is>
       </c>
       <c r="G1090" t="n">
@@ -34235,24 +34235,24 @@
         </is>
       </c>
       <c r="B1091" s="2" t="n">
-        <v>46083.33333333334</v>
+        <v>46065.58333333334</v>
       </c>
       <c r="C1091" s="2" t="n">
-        <v>46087.5</v>
+        <v>46065.71875</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
-          <t>CAJ-11</t>
+          <t>COQ-07</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
-          <t>APR - PT</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1091" t="n">
@@ -34266,14 +34266,14 @@
         </is>
       </c>
       <c r="B1092" s="2" t="n">
-        <v>46090.33333333334</v>
+        <v>46073.33333333334</v>
       </c>
       <c r="C1092" s="2" t="n">
-        <v>46090.5</v>
+        <v>46073.5</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t>BUR-17</t>
+          <t>CAJ-05</t>
         </is>
       </c>
       <c r="E1092" t="inlineStr">
@@ -34297,19 +34297,19 @@
         </is>
       </c>
       <c r="B1093" s="2" t="n">
-        <v>46091.375</v>
+        <v>46076.54166666666</v>
       </c>
       <c r="C1093" s="2" t="n">
-        <v>46091.625</v>
+        <v>46076.69722222222</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
-          <t>MOR-02</t>
+          <t>CAJ-13</t>
         </is>
       </c>
       <c r="E1093" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1093" t="inlineStr">
@@ -34328,24 +34328,24 @@
         </is>
       </c>
       <c r="B1094" s="2" t="n">
-        <v>46091.41666666666</v>
+        <v>46076.66180555556</v>
       </c>
       <c r="C1094" s="2" t="n">
-        <v>46091.66666666666</v>
+        <v>46076.70347222222</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
-          <t>MOR-02</t>
+          <t>PPG-86</t>
         </is>
       </c>
       <c r="E1094" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1094" t="n">
@@ -34359,24 +34359,24 @@
         </is>
       </c>
       <c r="B1095" s="2" t="n">
-        <v>46091.54166666666</v>
+        <v>46076.69444444445</v>
       </c>
       <c r="C1095" s="2" t="n">
-        <v>46091.70902777778</v>
+        <v>46076.70416666667</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
-          <t>MOR-02</t>
+          <t>PPG-12</t>
         </is>
       </c>
       <c r="E1095" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1095" t="n">
@@ -34390,19 +34390,19 @@
         </is>
       </c>
       <c r="B1096" s="2" t="n">
-        <v>46091.66666666666</v>
+        <v>46079.375</v>
       </c>
       <c r="C1096" s="2" t="n">
-        <v>46091.75</v>
+        <v>46079.5</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>MOR-02</t>
+          <t>BUR-01</t>
         </is>
       </c>
       <c r="E1096" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1096" t="inlineStr">
@@ -34421,24 +34421,24 @@
         </is>
       </c>
       <c r="B1097" s="2" t="n">
-        <v>46092</v>
+        <v>46083.33333333334</v>
       </c>
       <c r="C1097" s="2" t="n">
-        <v>46092.625</v>
+        <v>46087.5</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
-          <t>QXB-24</t>
+          <t>CAJ-11</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>APR - PT</t>
         </is>
       </c>
       <c r="G1097" t="n">
@@ -34452,24 +34452,24 @@
         </is>
       </c>
       <c r="B1098" s="2" t="n">
-        <v>46092</v>
+        <v>46090.33333333334</v>
       </c>
       <c r="C1098" s="2" t="n">
-        <v>46092.625</v>
+        <v>46090.5</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
-          <t>QXB-25</t>
+          <t>BUR-17</t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1098" t="n">
@@ -34483,24 +34483,24 @@
         </is>
       </c>
       <c r="B1099" s="2" t="n">
-        <v>46092.33333333334</v>
+        <v>46091.375</v>
       </c>
       <c r="C1099" s="2" t="n">
-        <v>46092.35300925926</v>
+        <v>46091.625</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
-          <t>QXB-42</t>
+          <t>MOR-02</t>
         </is>
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1099" t="n">
@@ -34514,24 +34514,24 @@
         </is>
       </c>
       <c r="B1100" s="2" t="n">
-        <v>46092.33333333334</v>
+        <v>46091.41666666666</v>
       </c>
       <c r="C1100" s="2" t="n">
-        <v>46092.35416666666</v>
+        <v>46091.66666666666</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
-          <t>QXB-03</t>
+          <t>MOR-02</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1100" t="n">
@@ -34545,24 +34545,24 @@
         </is>
       </c>
       <c r="B1101" s="2" t="n">
-        <v>46092.33333333334</v>
+        <v>46091.54166666666</v>
       </c>
       <c r="C1101" s="2" t="n">
-        <v>46092.35416666666</v>
+        <v>46091.70902777778</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
-          <t>QXB-23</t>
+          <t>MOR-02</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1101" t="n">
@@ -34576,24 +34576,24 @@
         </is>
       </c>
       <c r="B1102" s="2" t="n">
-        <v>46092.33333333334</v>
+        <v>46091.66666666666</v>
       </c>
       <c r="C1102" s="2" t="n">
-        <v>46092.35416666666</v>
+        <v>46091.75</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
-          <t>QXB-27</t>
+          <t>MOR-02</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
         <is>
-          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
-          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1102" t="n">
@@ -34607,14 +34607,14 @@
         </is>
       </c>
       <c r="B1103" s="2" t="n">
-        <v>46092.33333333334</v>
+        <v>46092</v>
       </c>
       <c r="C1103" s="2" t="n">
-        <v>46092.35416666666</v>
+        <v>46092.625</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
-          <t>QXB-36</t>
+          <t>QXB-24</t>
         </is>
       </c>
       <c r="E1103" t="inlineStr">
@@ -34638,14 +34638,14 @@
         </is>
       </c>
       <c r="B1104" s="2" t="n">
-        <v>46092.33333333334</v>
+        <v>46092</v>
       </c>
       <c r="C1104" s="2" t="n">
-        <v>46092.35416666666</v>
+        <v>46092.625</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
-          <t>QXB-37</t>
+          <t>QXB-25</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
@@ -34672,11 +34672,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1105" s="2" t="n">
-        <v>46092.35416666666</v>
+        <v>46092.35300925926</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
-          <t>QXB-39</t>
+          <t>QXB-42</t>
         </is>
       </c>
       <c r="E1105" t="inlineStr">
@@ -34707,7 +34707,7 @@
       </c>
       <c r="D1106" t="inlineStr">
         <is>
-          <t>QXB-43</t>
+          <t>QXB-03</t>
         </is>
       </c>
       <c r="E1106" t="inlineStr">
@@ -34721,7 +34721,7 @@
         </is>
       </c>
       <c r="G1106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1107">
@@ -34738,7 +34738,7 @@
       </c>
       <c r="D1107" t="inlineStr">
         <is>
-          <t>QXB-52</t>
+          <t>QXB-23</t>
         </is>
       </c>
       <c r="E1107" t="inlineStr">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="D1108" t="inlineStr">
         <is>
-          <t>QXB-59</t>
+          <t>QXB-27</t>
         </is>
       </c>
       <c r="E1108" t="inlineStr">
@@ -34800,7 +34800,7 @@
       </c>
       <c r="D1109" t="inlineStr">
         <is>
-          <t>QXB-63</t>
+          <t>QXB-36</t>
         </is>
       </c>
       <c r="E1109" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>QXB-75</t>
+          <t>QXB-37</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="D1111" t="inlineStr">
         <is>
-          <t>QXB-81</t>
+          <t>QXB-39</t>
         </is>
       </c>
       <c r="E1111" t="inlineStr">
@@ -34893,7 +34893,7 @@
       </c>
       <c r="D1112" t="inlineStr">
         <is>
-          <t>QXB-97</t>
+          <t>QXB-43</t>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
@@ -34907,7 +34907,7 @@
         </is>
       </c>
       <c r="G1112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1113">
@@ -34924,7 +34924,7 @@
       </c>
       <c r="D1113" t="inlineStr">
         <is>
-          <t>QXB-MV</t>
+          <t>QXB-52</t>
         </is>
       </c>
       <c r="E1113" t="inlineStr">
@@ -34938,7 +34938,7 @@
         </is>
       </c>
       <c r="G1113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1114">
@@ -34951,11 +34951,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1114" s="2" t="n">
-        <v>46092.36111111111</v>
+        <v>46092.35416666666</v>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
-          <t>QXB-19</t>
+          <t>QXB-59</t>
         </is>
       </c>
       <c r="E1114" t="inlineStr">
@@ -34982,11 +34982,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1115" s="2" t="n">
-        <v>46092.36111111111</v>
+        <v>46092.35416666666</v>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>QXB-93</t>
+          <t>QXB-63</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -35013,11 +35013,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1116" s="2" t="n">
-        <v>46092.36111111111</v>
+        <v>46092.35416666666</v>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
-          <t>QXB-MV</t>
+          <t>QXB-75</t>
         </is>
       </c>
       <c r="E1116" t="inlineStr">
@@ -35044,11 +35044,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1117" s="2" t="n">
-        <v>46092.36111111111</v>
+        <v>46092.35416666666</v>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
-          <t>QXB-WS</t>
+          <t>QXB-81</t>
         </is>
       </c>
       <c r="E1117" t="inlineStr">
@@ -35075,11 +35075,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1118" s="2" t="n">
-        <v>46092.36805555555</v>
+        <v>46092.35416666666</v>
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>QXB-20</t>
+          <t>QXB-97</t>
         </is>
       </c>
       <c r="E1118" t="inlineStr">
@@ -35106,11 +35106,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1119" s="2" t="n">
-        <v>46092.39583333334</v>
+        <v>46092.35416666666</v>
       </c>
       <c r="D1119" t="inlineStr">
         <is>
-          <t>QXB-06</t>
+          <t>QXB-MV</t>
         </is>
       </c>
       <c r="E1119" t="inlineStr">
@@ -35124,7 +35124,7 @@
         </is>
       </c>
       <c r="G1119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1120">
@@ -35137,11 +35137,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1120" s="2" t="n">
-        <v>46092.39583333334</v>
+        <v>46092.36111111111</v>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
-          <t>QXB-18</t>
+          <t>QXB-19</t>
         </is>
       </c>
       <c r="E1120" t="inlineStr">
@@ -35168,11 +35168,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1121" s="2" t="n">
-        <v>46092.39583333334</v>
+        <v>46092.36111111111</v>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>QXB-38</t>
+          <t>QXB-93</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
@@ -35199,11 +35199,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1122" s="2" t="n">
-        <v>46092.39583333334</v>
+        <v>46092.36111111111</v>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>QXB-83</t>
+          <t>QXB-MV</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
@@ -35230,11 +35230,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1123" s="2" t="n">
-        <v>46092.41666666666</v>
+        <v>46092.36111111111</v>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>QXB-28</t>
+          <t>QXB-WS</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
@@ -35261,11 +35261,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1124" s="2" t="n">
-        <v>46092.41666666666</v>
+        <v>46092.36805555555</v>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>QXB-64</t>
+          <t>QXB-20</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
@@ -35279,7 +35279,7 @@
         </is>
       </c>
       <c r="G1124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1125">
@@ -35292,11 +35292,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1125" s="2" t="n">
-        <v>46092.41666666666</v>
+        <v>46092.39583333334</v>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>QXB-72</t>
+          <t>QXB-06</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
@@ -35323,11 +35323,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1126" s="2" t="n">
-        <v>46092.41666666666</v>
+        <v>46092.39583333334</v>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>QXB-MV</t>
+          <t>QXB-18</t>
         </is>
       </c>
       <c r="E1126" t="inlineStr">
@@ -35354,11 +35354,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1127" s="2" t="n">
-        <v>46092.45833333334</v>
+        <v>46092.39583333334</v>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>QXB-31</t>
+          <t>QXB-38</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
@@ -35385,11 +35385,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1128" s="2" t="n">
-        <v>46092.5</v>
+        <v>46092.39583333334</v>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>QXB-33</t>
+          <t>QXB-83</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
@@ -35416,11 +35416,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1129" s="2" t="n">
-        <v>46092.54166666666</v>
+        <v>46092.41666666666</v>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
-          <t>QXB-05</t>
+          <t>QXB-28</t>
         </is>
       </c>
       <c r="E1129" t="inlineStr">
@@ -35447,11 +35447,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1130" s="2" t="n">
-        <v>46092.625</v>
+        <v>46092.41666666666</v>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>QXB-43</t>
+          <t>QXB-64</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="G1130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1131">
@@ -35478,11 +35478,11 @@
         <v>46092.33333333334</v>
       </c>
       <c r="C1131" s="2" t="n">
-        <v>46092.625</v>
+        <v>46092.41666666666</v>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>QXB-4K</t>
+          <t>QXB-72</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
@@ -35506,14 +35506,14 @@
         </is>
       </c>
       <c r="B1132" s="2" t="n">
-        <v>46092.4375</v>
+        <v>46092.33333333334</v>
       </c>
       <c r="C1132" s="2" t="n">
-        <v>46092.46319444444</v>
+        <v>46092.41666666666</v>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>QXB-06</t>
+          <t>QXB-MV</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
@@ -35537,14 +35537,14 @@
         </is>
       </c>
       <c r="B1133" s="2" t="n">
-        <v>46093.67083333333</v>
+        <v>46092.33333333334</v>
       </c>
       <c r="C1133" s="2" t="n">
-        <v>46093.70833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>QXB-MV</t>
+          <t>QXB-31</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
@@ -35568,24 +35568,24 @@
         </is>
       </c>
       <c r="B1134" s="2" t="n">
-        <v>46098.33333333334</v>
+        <v>46092.33333333334</v>
       </c>
       <c r="C1134" s="2" t="n">
-        <v>46098.625</v>
+        <v>46092.5</v>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>CAJ-11</t>
+          <t>QXB-33</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
         <is>
-          <t>IMPLANTAÇÕES/MELHORIAS</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1134" t="n">
@@ -35599,24 +35599,24 @@
         </is>
       </c>
       <c r="B1135" s="2" t="n">
-        <v>46099.375</v>
+        <v>46092.33333333334</v>
       </c>
       <c r="C1135" s="2" t="n">
-        <v>46099.37777777778</v>
+        <v>46092.54166666666</v>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
-          <t>MOR-OL</t>
+          <t>QXB-05</t>
         </is>
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>PARQUE EÓLICO</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
         <is>
-          <t>APR - PT</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1135" t="n">
@@ -35630,24 +35630,24 @@
         </is>
       </c>
       <c r="B1136" s="2" t="n">
-        <v>46099.375</v>
+        <v>46092.33333333334</v>
       </c>
       <c r="C1136" s="2" t="n">
-        <v>46099.38888888889</v>
+        <v>46092.625</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
-          <t>MOR-08</t>
+          <t>QXB-43</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1136" t="n">
@@ -35661,24 +35661,24 @@
         </is>
       </c>
       <c r="B1137" s="2" t="n">
-        <v>46099.41666666666</v>
+        <v>46092.33333333334</v>
       </c>
       <c r="C1137" s="2" t="n">
-        <v>46099.43055555555</v>
+        <v>46092.625</v>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
-          <t>MOR-03</t>
+          <t>QXB-4K</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1137" t="n">
@@ -35692,24 +35692,24 @@
         </is>
       </c>
       <c r="B1138" s="2" t="n">
-        <v>46099.41666666666</v>
+        <v>46092.4375</v>
       </c>
       <c r="C1138" s="2" t="n">
-        <v>46099.44722222222</v>
+        <v>46092.46319444444</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>QXB-06</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1138" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1138" t="n">
@@ -35723,24 +35723,24 @@
         </is>
       </c>
       <c r="B1139" s="2" t="n">
-        <v>46099.45833333334</v>
+        <v>46093.67083333333</v>
       </c>
       <c r="C1139" s="2" t="n">
-        <v>46099.47916666666</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
-          <t>MOR-06</t>
+          <t>QXB-MV</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>FERRAMENTAS EQUIPAMENTOS DE ENSAIO E MEDIÇÃO</t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>MPP6 - AUDITORIA DE FERRAMENTAS - M6</t>
         </is>
       </c>
       <c r="G1139" t="n">
@@ -35754,14 +35754,14 @@
         </is>
       </c>
       <c r="B1140" s="2" t="n">
-        <v>46099.47916666666</v>
+        <v>46098.33333333334</v>
       </c>
       <c r="C1140" s="2" t="n">
-        <v>46099.48194444444</v>
+        <v>46098.625</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
-          <t>MOR-02</t>
+          <t>CAJ-11</t>
         </is>
       </c>
       <c r="E1140" t="inlineStr">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="F1140" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>IMPLANTAÇÕES/MELHORIAS</t>
         </is>
       </c>
       <c r="G1140" t="n">
@@ -35785,24 +35785,24 @@
         </is>
       </c>
       <c r="B1141" s="2" t="n">
-        <v>46099.48055555556</v>
+        <v>46099.375</v>
       </c>
       <c r="C1141" s="2" t="n">
-        <v>46099.5</v>
+        <v>46099.37777777778</v>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
-          <t>MOR-01</t>
+          <t>MOR-OL</t>
         </is>
       </c>
       <c r="E1141" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>PARQUE EÓLICO</t>
         </is>
       </c>
       <c r="F1141" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>APR - PT</t>
         </is>
       </c>
       <c r="G1141" t="n">
@@ -35816,14 +35816,14 @@
         </is>
       </c>
       <c r="B1142" s="2" t="n">
-        <v>46099.48611111111</v>
+        <v>46099.375</v>
       </c>
       <c r="C1142" s="2" t="n">
-        <v>46099.49236111111</v>
+        <v>46099.38888888889</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
-          <t>MOR-07</t>
+          <t>MOR-08</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
@@ -35847,19 +35847,19 @@
         </is>
       </c>
       <c r="B1143" s="2" t="n">
-        <v>46099.54166666666</v>
+        <v>46099.375</v>
       </c>
       <c r="C1143" s="2" t="n">
-        <v>46099.55972222222</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>MOR-05</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
@@ -35878,19 +35878,19 @@
         </is>
       </c>
       <c r="B1144" s="2" t="n">
-        <v>46099.54166666666</v>
+        <v>46099.375</v>
       </c>
       <c r="C1144" s="2" t="n">
-        <v>46099.56944444445</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>MOR-04</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
@@ -35909,19 +35909,19 @@
         </is>
       </c>
       <c r="B1145" s="2" t="n">
-        <v>46099.58333333334</v>
+        <v>46099.375</v>
       </c>
       <c r="C1145" s="2" t="n">
-        <v>46099.60069444445</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
@@ -35940,19 +35940,19 @@
         </is>
       </c>
       <c r="B1146" s="2" t="n">
-        <v>46099.58333333334</v>
+        <v>46099.375</v>
       </c>
       <c r="C1146" s="2" t="n">
-        <v>46099.60972222222</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>MOR-09</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
@@ -35971,24 +35971,24 @@
         </is>
       </c>
       <c r="B1147" s="2" t="n">
-        <v>46104.54166666666</v>
+        <v>46099.375</v>
       </c>
       <c r="C1147" s="2" t="n">
-        <v>46104.55347222222</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1147" t="inlineStr">
         <is>
-          <t>MOR-OL</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>PARQUE EÓLICO</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
         <is>
-          <t>APR - PT</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1147" t="n">
@@ -36002,19 +36002,19 @@
         </is>
       </c>
       <c r="B1148" s="2" t="n">
-        <v>46104.58333333334</v>
+        <v>46099.375</v>
       </c>
       <c r="C1148" s="2" t="n">
-        <v>46104.59722222222</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>MOR-19</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1148" t="inlineStr">
@@ -36033,19 +36033,19 @@
         </is>
       </c>
       <c r="B1149" s="2" t="n">
-        <v>46104.59791666667</v>
+        <v>46099.375</v>
       </c>
       <c r="C1149" s="2" t="n">
-        <v>46104.61388888889</v>
+        <v>46099.60416666666</v>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1149" t="inlineStr">
@@ -36064,14 +36064,14 @@
         </is>
       </c>
       <c r="B1150" s="2" t="n">
-        <v>46104.60347222222</v>
+        <v>46099.41666666666</v>
       </c>
       <c r="C1150" s="2" t="n">
-        <v>46104.61944444444</v>
+        <v>46099.43055555555</v>
       </c>
       <c r="D1150" t="inlineStr">
         <is>
-          <t>MOR-16</t>
+          <t>MOR-03</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
@@ -36095,14 +36095,14 @@
         </is>
       </c>
       <c r="B1151" s="2" t="n">
-        <v>46104.60416666666</v>
+        <v>46099.41666666666</v>
       </c>
       <c r="C1151" s="2" t="n">
-        <v>46104.61736111111</v>
+        <v>46099.44722222222</v>
       </c>
       <c r="D1151" t="inlineStr">
         <is>
-          <t>MOR-17</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1151" t="inlineStr">
@@ -36126,14 +36126,14 @@
         </is>
       </c>
       <c r="B1152" s="2" t="n">
-        <v>46104.60763888889</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="C1152" s="2" t="n">
-        <v>46104.62152777778</v>
+        <v>46099.47916666666</v>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>MOR-15</t>
+          <t>MOR-06</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
@@ -36157,14 +36157,14 @@
         </is>
       </c>
       <c r="B1153" s="2" t="n">
-        <v>46104.61805555555</v>
+        <v>46099.47916666666</v>
       </c>
       <c r="C1153" s="2" t="n">
-        <v>46104.63194444445</v>
+        <v>46099.48194444444</v>
       </c>
       <c r="D1153" t="inlineStr">
         <is>
-          <t>MOR-12</t>
+          <t>MOR-02</t>
         </is>
       </c>
       <c r="E1153" t="inlineStr">
@@ -36188,14 +36188,14 @@
         </is>
       </c>
       <c r="B1154" s="2" t="n">
-        <v>46104.64583333334</v>
+        <v>46099.48055555556</v>
       </c>
       <c r="C1154" s="2" t="n">
-        <v>46104.66111111111</v>
+        <v>46099.5</v>
       </c>
       <c r="D1154" t="inlineStr">
         <is>
-          <t>MOR-13</t>
+          <t>MOR-01</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
@@ -36219,14 +36219,14 @@
         </is>
       </c>
       <c r="B1155" s="2" t="n">
-        <v>46104.66041666667</v>
+        <v>46099.48611111111</v>
       </c>
       <c r="C1155" s="2" t="n">
-        <v>46104.66111111111</v>
+        <v>46099.49236111111</v>
       </c>
       <c r="D1155" t="inlineStr">
         <is>
-          <t>MOR-14</t>
+          <t>MOR-07</t>
         </is>
       </c>
       <c r="E1155" t="inlineStr">
@@ -36250,24 +36250,24 @@
         </is>
       </c>
       <c r="B1156" s="2" t="n">
-        <v>46111.33333333334</v>
+        <v>46099.54166666666</v>
       </c>
       <c r="C1156" s="2" t="n">
-        <v>46111.375</v>
+        <v>46099.55972222222</v>
       </c>
       <c r="D1156" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-05</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1156" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1156" t="n">
@@ -36281,24 +36281,24 @@
         </is>
       </c>
       <c r="B1157" s="2" t="n">
-        <v>46111.41666666666</v>
+        <v>46099.54166666666</v>
       </c>
       <c r="C1157" s="2" t="n">
-        <v>46112.50069444445</v>
+        <v>46099.56944444445</v>
       </c>
       <c r="D1157" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>MOR-04</t>
         </is>
       </c>
       <c r="E1157" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1157" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1157" t="n">
@@ -36312,24 +36312,24 @@
         </is>
       </c>
       <c r="B1158" s="2" t="n">
-        <v>46111.45833333334</v>
+        <v>46099.58333333334</v>
       </c>
       <c r="C1158" s="2" t="n">
-        <v>46112.41666666666</v>
+        <v>46099.60069444445</v>
       </c>
       <c r="D1158" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1158" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1158" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1158" t="n">
@@ -36343,24 +36343,24 @@
         </is>
       </c>
       <c r="B1159" s="2" t="n">
-        <v>46111.48333333333</v>
+        <v>46099.58333333334</v>
       </c>
       <c r="C1159" s="2" t="n">
-        <v>46112.5</v>
+        <v>46099.60972222222</v>
       </c>
       <c r="D1159" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>MOR-09</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1159" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1159" t="n">
@@ -36374,24 +36374,24 @@
         </is>
       </c>
       <c r="B1160" s="2" t="n">
-        <v>46111.52569444444</v>
+        <v>46104.54166666666</v>
       </c>
       <c r="C1160" s="2" t="n">
-        <v>46112.5</v>
+        <v>46104.55347222222</v>
       </c>
       <c r="D1160" t="inlineStr">
         <is>
-          <t>MOR-11</t>
+          <t>MOR-OL</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>PARQUE EÓLICO</t>
         </is>
       </c>
       <c r="F1160" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>APR - PT</t>
         </is>
       </c>
       <c r="G1160" t="n">
@@ -36405,14 +36405,14 @@
         </is>
       </c>
       <c r="B1161" s="2" t="n">
-        <v>46113.33333333334</v>
+        <v>46104.58333333334</v>
       </c>
       <c r="C1161" s="2" t="n">
-        <v>46113.4125</v>
+        <v>46104.59722222222</v>
       </c>
       <c r="D1161" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-19</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
@@ -36422,7 +36422,7 @@
       </c>
       <c r="F1161" t="inlineStr">
         <is>
-          <t>APR - PT</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1161" t="n">
@@ -36436,14 +36436,14 @@
         </is>
       </c>
       <c r="B1162" s="2" t="n">
-        <v>46113.33333333334</v>
+        <v>46104.59791666667</v>
       </c>
       <c r="C1162" s="2" t="n">
-        <v>46113.5</v>
+        <v>46104.61388888889</v>
       </c>
       <c r="D1162" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-18</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="F1162" t="inlineStr">
         <is>
-          <t>COLETA DE DADOS DE ATIVOS</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1162" t="n">
@@ -36467,24 +36467,24 @@
         </is>
       </c>
       <c r="B1163" s="2" t="n">
-        <v>46113.45138888889</v>
+        <v>46104.60347222222</v>
       </c>
       <c r="C1163" s="2" t="n">
-        <v>46113.46041666667</v>
+        <v>46104.61944444444</v>
       </c>
       <c r="D1163" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-16</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1163" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1163" t="n">
@@ -36498,24 +36498,24 @@
         </is>
       </c>
       <c r="B1164" s="2" t="n">
-        <v>46113.58333333334</v>
+        <v>46104.60416666666</v>
       </c>
       <c r="C1164" s="2" t="n">
-        <v>46113.62638888889</v>
+        <v>46104.61736111111</v>
       </c>
       <c r="D1164" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-17</t>
         </is>
       </c>
       <c r="E1164" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1164" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1164" t="n">
@@ -36529,24 +36529,24 @@
         </is>
       </c>
       <c r="B1165" s="2" t="n">
-        <v>46113.58333333334</v>
+        <v>46104.60763888889</v>
       </c>
       <c r="C1165" s="2" t="n">
-        <v>46113.66666666666</v>
+        <v>46104.62152777778</v>
       </c>
       <c r="D1165" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-15</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1165" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1165" t="n">
@@ -36560,24 +36560,24 @@
         </is>
       </c>
       <c r="B1166" s="2" t="n">
-        <v>46113.62430555555</v>
+        <v>46104.61805555555</v>
       </c>
       <c r="C1166" s="2" t="n">
-        <v>46113.70833333334</v>
+        <v>46104.63194444445</v>
       </c>
       <c r="D1166" t="inlineStr">
         <is>
-          <t>MOR-10</t>
+          <t>MOR-12</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1166" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1166" t="n">
@@ -36591,24 +36591,24 @@
         </is>
       </c>
       <c r="B1167" s="2" t="n">
-        <v>46113.625</v>
+        <v>46104.64583333334</v>
       </c>
       <c r="C1167" s="2" t="n">
-        <v>46113.66666666666</v>
+        <v>46104.66111111111</v>
       </c>
       <c r="D1167" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>MOR-13</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1167" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1167" t="n">
@@ -36622,24 +36622,24 @@
         </is>
       </c>
       <c r="B1168" s="2" t="n">
-        <v>46118.33333333334</v>
+        <v>46104.66041666667</v>
       </c>
       <c r="C1168" s="2" t="n">
-        <v>46118.38125</v>
+        <v>46104.66111111111</v>
       </c>
       <c r="D1168" t="inlineStr">
         <is>
-          <t>COQ-OL</t>
+          <t>MOR-14</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>PARQUE EÓLICO</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1168" t="inlineStr">
         <is>
-          <t>APR - PT</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1168" t="n">
@@ -36653,24 +36653,24 @@
         </is>
       </c>
       <c r="B1169" s="2" t="n">
-        <v>46118.41666666666</v>
+        <v>46111.33333333334</v>
       </c>
       <c r="C1169" s="2" t="n">
-        <v>46118.44097222222</v>
+        <v>46111.375</v>
       </c>
       <c r="D1169" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1169" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G1169" t="n">
@@ -36684,24 +36684,24 @@
         </is>
       </c>
       <c r="B1170" s="2" t="n">
-        <v>46118.45833333334</v>
+        <v>46111.41666666666</v>
       </c>
       <c r="C1170" s="2" t="n">
-        <v>46118.47430555556</v>
+        <v>46112.50069444445</v>
       </c>
       <c r="D1170" t="inlineStr">
         <is>
-          <t>COQ-18</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1170" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1170" t="n">
@@ -36715,24 +36715,24 @@
         </is>
       </c>
       <c r="B1171" s="2" t="n">
-        <v>46118.45833333334</v>
+        <v>46111.45833333334</v>
       </c>
       <c r="C1171" s="2" t="n">
-        <v>46118.48611111111</v>
+        <v>46112.41666666666</v>
       </c>
       <c r="D1171" t="inlineStr">
         <is>
-          <t>COQ-16</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>AEROGERADOR</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1171" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1171" t="n">
@@ -36746,14 +36746,14 @@
         </is>
       </c>
       <c r="B1172" s="2" t="n">
-        <v>46119.38194444445</v>
+        <v>46111.48333333333</v>
       </c>
       <c r="C1172" s="2" t="n">
-        <v>46119.38611111111</v>
+        <v>46112.5</v>
       </c>
       <c r="D1172" t="inlineStr">
         <is>
-          <t>COQ-18</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1172" t="inlineStr">
@@ -36763,7 +36763,7 @@
       </c>
       <c r="F1172" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1172" t="n">
@@ -36777,24 +36777,24 @@
         </is>
       </c>
       <c r="B1173" s="2" t="n">
-        <v>46119.41666666666</v>
+        <v>46111.52569444444</v>
       </c>
       <c r="C1173" s="2" t="n">
-        <v>46119.41944444444</v>
+        <v>46112.5</v>
       </c>
       <c r="D1173" t="inlineStr">
         <is>
-          <t>COQ-16</t>
+          <t>MOR-11</t>
         </is>
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1173" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1173" t="n">
@@ -36808,24 +36808,24 @@
         </is>
       </c>
       <c r="B1174" s="2" t="n">
-        <v>46119.41666666666</v>
+        <v>46113.33333333334</v>
       </c>
       <c r="C1174" s="2" t="n">
-        <v>46119.42361111111</v>
+        <v>46113.4125</v>
       </c>
       <c r="D1174" t="inlineStr">
         <is>
-          <t>COQ-16</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1174" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>APR - PT</t>
         </is>
       </c>
       <c r="G1174" t="n">
@@ -36839,24 +36839,24 @@
         </is>
       </c>
       <c r="B1175" s="2" t="n">
-        <v>46119.41666666666</v>
+        <v>46113.33333333334</v>
       </c>
       <c r="C1175" s="2" t="n">
-        <v>46119.42361111111</v>
+        <v>46113.5</v>
       </c>
       <c r="D1175" t="inlineStr">
         <is>
-          <t>COQ-18</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1175" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>COLETA DE DADOS DE ATIVOS</t>
         </is>
       </c>
       <c r="G1175" t="n">
@@ -36870,24 +36870,24 @@
         </is>
       </c>
       <c r="B1176" s="2" t="n">
-        <v>46119.41666666666</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="C1176" s="2" t="n">
-        <v>46119.4375</v>
+        <v>46113.46041666667</v>
       </c>
       <c r="D1176" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1176" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G1176" t="n">
@@ -36901,24 +36901,24 @@
         </is>
       </c>
       <c r="B1177" s="2" t="n">
-        <v>46119.43055555555</v>
+        <v>46113.58333333334</v>
       </c>
       <c r="C1177" s="2" t="n">
-        <v>46119.44097222222</v>
+        <v>46113.62638888889</v>
       </c>
       <c r="D1177" t="inlineStr">
         <is>
-          <t>COQ-16</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1177" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G1177" t="n">
@@ -36932,24 +36932,24 @@
         </is>
       </c>
       <c r="B1178" s="2" t="n">
-        <v>46119.44375</v>
+        <v>46113.58333333334</v>
       </c>
       <c r="C1178" s="2" t="n">
-        <v>46119.45694444444</v>
+        <v>46113.66666666666</v>
       </c>
       <c r="D1178" t="inlineStr">
         <is>
-          <t>COQ-18</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1178" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G1178" t="n">
@@ -36963,24 +36963,24 @@
         </is>
       </c>
       <c r="B1179" s="2" t="n">
-        <v>46119.44652777778</v>
+        <v>46113.62430555555</v>
       </c>
       <c r="C1179" s="2" t="n">
-        <v>46119.44791666666</v>
+        <v>46113.70833333334</v>
       </c>
       <c r="D1179" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>MOR-10</t>
         </is>
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE QUALIDADE DE AEROGERADOR</t>
         </is>
       </c>
       <c r="G1179" t="n">
@@ -36994,24 +36994,24 @@
         </is>
       </c>
       <c r="B1180" s="2" t="n">
-        <v>46119.44722222222</v>
+        <v>46113.625</v>
       </c>
       <c r="C1180" s="2" t="n">
-        <v>46119.45416666667</v>
+        <v>46113.66666666666</v>
       </c>
       <c r="D1180" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>MOR-18</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1180" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
       <c r="G1180" t="n">
@@ -37025,24 +37025,24 @@
         </is>
       </c>
       <c r="B1181" s="2" t="n">
-        <v>46119.44791666666</v>
+        <v>46118.33333333334</v>
       </c>
       <c r="C1181" s="2" t="n">
-        <v>46119.45486111111</v>
+        <v>46118.38125</v>
       </c>
       <c r="D1181" t="inlineStr">
         <is>
-          <t>COQ-15</t>
+          <t>COQ-OL</t>
         </is>
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>PARQUE EÓLICO</t>
         </is>
       </c>
       <c r="F1181" t="inlineStr">
         <is>
-          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+          <t>APR - PT</t>
         </is>
       </c>
       <c r="G1181" t="n">
@@ -37056,19 +37056,19 @@
         </is>
       </c>
       <c r="B1182" s="2" t="n">
-        <v>46119.44791666666</v>
+        <v>46118.41666666666</v>
       </c>
       <c r="C1182" s="2" t="n">
-        <v>46119.45555555556</v>
+        <v>46118.44097222222</v>
       </c>
       <c r="D1182" t="inlineStr">
         <is>
-          <t>COQ-18</t>
+          <t>COQ-17</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1182" t="inlineStr">
@@ -37087,19 +37087,19 @@
         </is>
       </c>
       <c r="B1183" s="2" t="n">
-        <v>46119.45138888889</v>
+        <v>46118.45833333334</v>
       </c>
       <c r="C1183" s="2" t="n">
-        <v>46119.45277777778</v>
+        <v>46118.47430555556</v>
       </c>
       <c r="D1183" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>COQ-18</t>
         </is>
       </c>
       <c r="E1183" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1183" t="inlineStr">
@@ -37118,19 +37118,19 @@
         </is>
       </c>
       <c r="B1184" s="2" t="n">
-        <v>46119.45277777778</v>
+        <v>46118.45833333334</v>
       </c>
       <c r="C1184" s="2" t="n">
-        <v>46119.45347222222</v>
+        <v>46118.48611111111</v>
       </c>
       <c r="D1184" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>COQ-16</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>AEROGERADOR</t>
         </is>
       </c>
       <c r="F1184" t="inlineStr">
@@ -37149,10 +37149,10 @@
         </is>
       </c>
       <c r="B1185" s="2" t="n">
-        <v>46119.45486111111</v>
+        <v>46119.38194444445</v>
       </c>
       <c r="C1185" s="2" t="n">
-        <v>46119.45625</v>
+        <v>46119.38611111111</v>
       </c>
       <c r="D1185" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
       </c>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
@@ -37180,19 +37180,19 @@
         </is>
       </c>
       <c r="B1186" s="2" t="n">
-        <v>46119.54166666666</v>
+        <v>46119.41666666666</v>
       </c>
       <c r="C1186" s="2" t="n">
-        <v>46119.55416666667</v>
+        <v>46119.41944444444</v>
       </c>
       <c r="D1186" t="inlineStr">
         <is>
-          <t>COQ-15</t>
+          <t>COQ-16</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
@@ -37211,10 +37211,10 @@
         </is>
       </c>
       <c r="B1187" s="2" t="n">
-        <v>46119.54236111111</v>
+        <v>46119.41666666666</v>
       </c>
       <c r="C1187" s="2" t="n">
-        <v>46119.55</v>
+        <v>46119.42361111111</v>
       </c>
       <c r="D1187" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1187" t="inlineStr">
@@ -37242,19 +37242,19 @@
         </is>
       </c>
       <c r="B1188" s="2" t="n">
-        <v>46119.54791666667</v>
+        <v>46119.41666666666</v>
       </c>
       <c r="C1188" s="2" t="n">
-        <v>46119.55347222222</v>
+        <v>46119.42361111111</v>
       </c>
       <c r="D1188" t="inlineStr">
         <is>
-          <t>COQ-15</t>
+          <t>COQ-18</t>
         </is>
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1188" t="inlineStr">
@@ -37273,19 +37273,19 @@
         </is>
       </c>
       <c r="B1189" s="2" t="n">
-        <v>46119.54861111111</v>
+        <v>46119.41666666666</v>
       </c>
       <c r="C1189" s="2" t="n">
-        <v>46119.55208333334</v>
+        <v>46119.4375</v>
       </c>
       <c r="D1189" t="inlineStr">
         <is>
-          <t>COQ-15</t>
+          <t>COQ-17</t>
         </is>
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1189" t="inlineStr">
@@ -37304,10 +37304,10 @@
         </is>
       </c>
       <c r="B1190" s="2" t="n">
-        <v>46119.54861111111</v>
+        <v>46119.43055555555</v>
       </c>
       <c r="C1190" s="2" t="n">
-        <v>46119.55763888889</v>
+        <v>46119.44097222222</v>
       </c>
       <c r="D1190" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
       </c>
       <c r="E1190" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1190" t="inlineStr">
@@ -37335,19 +37335,19 @@
         </is>
       </c>
       <c r="B1191" s="2" t="n">
-        <v>46119.54930555556</v>
+        <v>46119.44375</v>
       </c>
       <c r="C1191" s="2" t="n">
-        <v>46119.55208333334</v>
+        <v>46119.45694444444</v>
       </c>
       <c r="D1191" t="inlineStr">
         <is>
-          <t>COQ-11</t>
+          <t>COQ-18</t>
         </is>
       </c>
       <c r="E1191" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1191" t="inlineStr">
@@ -37366,19 +37366,19 @@
         </is>
       </c>
       <c r="B1192" s="2" t="n">
-        <v>46119.54930555556</v>
+        <v>46119.44652777778</v>
       </c>
       <c r="C1192" s="2" t="n">
-        <v>46119.55208333334</v>
+        <v>46119.44791666666</v>
       </c>
       <c r="D1192" t="inlineStr">
         <is>
-          <t>COQ-11</t>
+          <t>COQ-17</t>
         </is>
       </c>
       <c r="E1192" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1192" t="inlineStr">
@@ -37397,19 +37397,19 @@
         </is>
       </c>
       <c r="B1193" s="2" t="n">
-        <v>46119.54930555556</v>
+        <v>46119.44722222222</v>
       </c>
       <c r="C1193" s="2" t="n">
-        <v>46119.55277777778</v>
+        <v>46119.45416666667</v>
       </c>
       <c r="D1193" t="inlineStr">
         <is>
-          <t>COQ-15</t>
+          <t>COQ-17</t>
         </is>
       </c>
       <c r="E1193" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1193" t="inlineStr">
@@ -37428,19 +37428,19 @@
         </is>
       </c>
       <c r="B1194" s="2" t="n">
-        <v>46119.55555555555</v>
+        <v>46119.44791666666</v>
       </c>
       <c r="C1194" s="2" t="n">
-        <v>46119.5625</v>
+        <v>46119.45486111111</v>
       </c>
       <c r="D1194" t="inlineStr">
         <is>
-          <t>COQ-11</t>
+          <t>COQ-15</t>
         </is>
       </c>
       <c r="E1194" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1194" t="inlineStr">
@@ -37459,19 +37459,19 @@
         </is>
       </c>
       <c r="B1195" s="2" t="n">
-        <v>46119.55902777778</v>
+        <v>46119.44791666666</v>
       </c>
       <c r="C1195" s="2" t="n">
-        <v>46119.56944444445</v>
+        <v>46119.45555555556</v>
       </c>
       <c r="D1195" t="inlineStr">
         <is>
-          <t>COQ-11</t>
+          <t>COQ-18</t>
         </is>
       </c>
       <c r="E1195" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1195" t="inlineStr">
@@ -37490,14 +37490,14 @@
         </is>
       </c>
       <c r="B1196" s="2" t="n">
-        <v>46119.58333333334</v>
+        <v>46119.45138888889</v>
       </c>
       <c r="C1196" s="2" t="n">
-        <v>46119.59097222222</v>
+        <v>46119.45277777778</v>
       </c>
       <c r="D1196" t="inlineStr">
         <is>
-          <t>COQ-14</t>
+          <t>COQ-17</t>
         </is>
       </c>
       <c r="E1196" t="inlineStr">
@@ -37521,14 +37521,14 @@
         </is>
       </c>
       <c r="B1197" s="2" t="n">
-        <v>46119.58680555555</v>
+        <v>46119.45277777778</v>
       </c>
       <c r="C1197" s="2" t="n">
-        <v>46119.63263888889</v>
+        <v>46119.45347222222</v>
       </c>
       <c r="D1197" t="inlineStr">
         <is>
-          <t>COQ-14</t>
+          <t>COQ-17</t>
         </is>
       </c>
       <c r="E1197" t="inlineStr">
@@ -37552,19 +37552,19 @@
         </is>
       </c>
       <c r="B1198" s="2" t="n">
-        <v>46119.59722222222</v>
+        <v>46119.45486111111</v>
       </c>
       <c r="C1198" s="2" t="n">
-        <v>46119.60069444445</v>
+        <v>46119.45625</v>
       </c>
       <c r="D1198" t="inlineStr">
         <is>
-          <t>COQ-14</t>
+          <t>COQ-18</t>
         </is>
       </c>
       <c r="E1198" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1198" t="inlineStr">
@@ -37583,19 +37583,19 @@
         </is>
       </c>
       <c r="B1199" s="2" t="n">
-        <v>46119.60069444445</v>
+        <v>46119.54166666666</v>
       </c>
       <c r="C1199" s="2" t="n">
-        <v>46119.60763888889</v>
+        <v>46119.55416666667</v>
       </c>
       <c r="D1199" t="inlineStr">
         <is>
-          <t>COQ-14</t>
+          <t>COQ-15</t>
         </is>
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1199" t="inlineStr">
@@ -37614,19 +37614,19 @@
         </is>
       </c>
       <c r="B1200" s="2" t="n">
-        <v>46119.625</v>
+        <v>46119.54236111111</v>
       </c>
       <c r="C1200" s="2" t="n">
-        <v>46119.62847222222</v>
+        <v>46119.55</v>
       </c>
       <c r="D1200" t="inlineStr">
         <is>
-          <t>COQ-13</t>
+          <t>COQ-16</t>
         </is>
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1200" t="inlineStr">
@@ -37645,19 +37645,19 @@
         </is>
       </c>
       <c r="B1201" s="2" t="n">
-        <v>46119.625</v>
+        <v>46119.54791666667</v>
       </c>
       <c r="C1201" s="2" t="n">
-        <v>46119.63194444445</v>
+        <v>46119.55347222222</v>
       </c>
       <c r="D1201" t="inlineStr">
         <is>
-          <t>COQ-13</t>
+          <t>COQ-15</t>
         </is>
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1201" t="inlineStr">
@@ -37676,14 +37676,14 @@
         </is>
       </c>
       <c r="B1202" s="2" t="n">
-        <v>46119.62847222222</v>
+        <v>46119.54861111111</v>
       </c>
       <c r="C1202" s="2" t="n">
-        <v>46119.63263888889</v>
+        <v>46119.55208333334</v>
       </c>
       <c r="D1202" t="inlineStr">
         <is>
-          <t>COQ-11</t>
+          <t>COQ-15</t>
         </is>
       </c>
       <c r="E1202" t="inlineStr">
@@ -37707,19 +37707,19 @@
         </is>
       </c>
       <c r="B1203" s="2" t="n">
-        <v>46119.63680555556</v>
+        <v>46119.54861111111</v>
       </c>
       <c r="C1203" s="2" t="n">
-        <v>46119.64513888889</v>
+        <v>46119.55763888889</v>
       </c>
       <c r="D1203" t="inlineStr">
         <is>
-          <t>COQ-14</t>
+          <t>COQ-16</t>
         </is>
       </c>
       <c r="E1203" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1203" t="inlineStr">
@@ -37738,19 +37738,19 @@
         </is>
       </c>
       <c r="B1204" s="2" t="n">
-        <v>46119.64236111111</v>
+        <v>46119.54930555556</v>
       </c>
       <c r="C1204" s="2" t="n">
-        <v>46119.65555555555</v>
+        <v>46119.55208333334</v>
       </c>
       <c r="D1204" t="inlineStr">
         <is>
-          <t>COQ-13</t>
+          <t>COQ-11</t>
         </is>
       </c>
       <c r="E1204" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1204" t="inlineStr">
@@ -37769,19 +37769,19 @@
         </is>
       </c>
       <c r="B1205" s="2" t="n">
-        <v>46119.65625</v>
+        <v>46119.54930555556</v>
       </c>
       <c r="C1205" s="2" t="n">
-        <v>46119.66388888889</v>
+        <v>46119.55208333334</v>
       </c>
       <c r="D1205" t="inlineStr">
         <is>
-          <t>COQ-13</t>
+          <t>COQ-11</t>
         </is>
       </c>
       <c r="E1205" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1205" t="inlineStr">
@@ -37800,19 +37800,19 @@
         </is>
       </c>
       <c r="B1206" s="2" t="n">
-        <v>46119.66666666666</v>
+        <v>46119.54930555556</v>
       </c>
       <c r="C1206" s="2" t="n">
-        <v>46119.67083333333</v>
+        <v>46119.55277777778</v>
       </c>
       <c r="D1206" t="inlineStr">
         <is>
-          <t>COQ-12</t>
+          <t>COQ-15</t>
         </is>
       </c>
       <c r="E1206" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1206" t="inlineStr">
@@ -37831,19 +37831,19 @@
         </is>
       </c>
       <c r="B1207" s="2" t="n">
-        <v>46119.67361111111</v>
+        <v>46119.55555555555</v>
       </c>
       <c r="C1207" s="2" t="n">
-        <v>46119.67708333334</v>
+        <v>46119.5625</v>
       </c>
       <c r="D1207" t="inlineStr">
         <is>
-          <t>COQ-12</t>
+          <t>COQ-11</t>
         </is>
       </c>
       <c r="E1207" t="inlineStr">
         <is>
-          <t>CONVERSOR</t>
+          <t>NACELLE</t>
         </is>
       </c>
       <c r="F1207" t="inlineStr">
@@ -37862,19 +37862,19 @@
         </is>
       </c>
       <c r="B1208" s="2" t="n">
-        <v>46119.67361111111</v>
+        <v>46119.55902777778</v>
       </c>
       <c r="C1208" s="2" t="n">
-        <v>46119.67708333334</v>
+        <v>46119.56944444445</v>
       </c>
       <c r="D1208" t="inlineStr">
         <is>
-          <t>COQ-12</t>
+          <t>COQ-11</t>
         </is>
       </c>
       <c r="E1208" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1208" t="inlineStr">
@@ -37893,19 +37893,19 @@
         </is>
       </c>
       <c r="B1209" s="2" t="n">
-        <v>46119.67361111111</v>
+        <v>46119.58333333334</v>
       </c>
       <c r="C1209" s="2" t="n">
-        <v>46119.6875</v>
+        <v>46119.59097222222</v>
       </c>
       <c r="D1209" t="inlineStr">
         <is>
-          <t>COQ-12</t>
+          <t>COQ-14</t>
         </is>
       </c>
       <c r="E1209" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1209" t="inlineStr">
@@ -37924,19 +37924,19 @@
         </is>
       </c>
       <c r="B1210" s="2" t="n">
-        <v>46119.68402777778</v>
+        <v>46119.58680555555</v>
       </c>
       <c r="C1210" s="2" t="n">
-        <v>46119.70069444444</v>
+        <v>46119.63263888889</v>
       </c>
       <c r="D1210" t="inlineStr">
         <is>
-          <t>COQ-12</t>
+          <t>COQ-14</t>
         </is>
       </c>
       <c r="E1210" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1210" t="inlineStr">
@@ -37955,19 +37955,19 @@
         </is>
       </c>
       <c r="B1211" s="2" t="n">
-        <v>46119.69930555556</v>
+        <v>46119.59722222222</v>
       </c>
       <c r="C1211" s="2" t="n">
-        <v>46119.70486111111</v>
+        <v>46119.60069444445</v>
       </c>
       <c r="D1211" t="inlineStr">
         <is>
-          <t>COQ-13</t>
+          <t>COQ-14</t>
         </is>
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>GERADOR</t>
         </is>
       </c>
       <c r="F1211" t="inlineStr">
@@ -37986,14 +37986,14 @@
         </is>
       </c>
       <c r="B1212" s="2" t="n">
-        <v>46120.375</v>
+        <v>46119.60069444445</v>
       </c>
       <c r="C1212" s="2" t="n">
-        <v>46120.62569444445</v>
+        <v>46119.60763888889</v>
       </c>
       <c r="D1212" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>COQ-14</t>
         </is>
       </c>
       <c r="E1212" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="F1212" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1212" t="n">
@@ -38017,24 +38017,24 @@
         </is>
       </c>
       <c r="B1213" s="2" t="n">
-        <v>46120.41666666666</v>
+        <v>46119.625</v>
       </c>
       <c r="C1213" s="2" t="n">
-        <v>46120.66666666666</v>
+        <v>46119.62847222222</v>
       </c>
       <c r="D1213" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>COQ-13</t>
         </is>
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>TORRE WTG</t>
+          <t>CONVERSOR</t>
         </is>
       </c>
       <c r="F1213" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1213" t="n">
@@ -38048,24 +38048,24 @@
         </is>
       </c>
       <c r="B1214" s="2" t="n">
-        <v>46120.45833333334</v>
+        <v>46119.625</v>
       </c>
       <c r="C1214" s="2" t="n">
-        <v>46120.58333333334</v>
+        <v>46119.63194444445</v>
       </c>
       <c r="D1214" t="inlineStr">
         <is>
-          <t>MOR-18</t>
+          <t>COQ-13</t>
         </is>
       </c>
       <c r="E1214" t="inlineStr">
         <is>
-          <t>GERADOR</t>
+          <t>SISTEMA PITCH</t>
         </is>
       </c>
       <c r="F1214" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1214" t="n">
@@ -38079,14 +38079,14 @@
         </is>
       </c>
       <c r="B1215" s="2" t="n">
-        <v>46122.33333333334</v>
+        <v>46119.62847222222</v>
       </c>
       <c r="C1215" s="2" t="n">
-        <v>46122.375</v>
+        <v>46119.63263888889</v>
       </c>
       <c r="D1215" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>COQ-11</t>
         </is>
       </c>
       <c r="E1215" t="inlineStr">
@@ -38096,7 +38096,7 @@
       </c>
       <c r="F1215" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1215" t="n">
@@ -38110,24 +38110,24 @@
         </is>
       </c>
       <c r="B1216" s="2" t="n">
-        <v>46122.33333333334</v>
+        <v>46119.63680555556</v>
       </c>
       <c r="C1216" s="2" t="n">
-        <v>46122.41666666666</v>
+        <v>46119.64513888889</v>
       </c>
       <c r="D1216" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>COQ-14</t>
         </is>
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>SISTEMA PITCH</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1216" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1216" t="n">
@@ -38141,24 +38141,24 @@
         </is>
       </c>
       <c r="B1217" s="2" t="n">
-        <v>46122.33333333334</v>
+        <v>46119.64236111111</v>
       </c>
       <c r="C1217" s="2" t="n">
-        <v>46122.5</v>
+        <v>46119.65555555555</v>
       </c>
       <c r="D1217" t="inlineStr">
         <is>
-          <t>COQ-17</t>
+          <t>COQ-13</t>
         </is>
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>NACELLE</t>
+          <t>TORRE WTG</t>
         </is>
       </c>
       <c r="F1217" t="inlineStr">
         <is>
-          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
         </is>
       </c>
       <c r="G1217" t="n">
@@ -38172,27 +38172,430 @@
         </is>
       </c>
       <c r="B1218" s="2" t="n">
+        <v>46119.65625</v>
+      </c>
+      <c r="C1218" s="2" t="n">
+        <v>46119.66388888889</v>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>COQ-13</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>GERADOR</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1219" s="2" t="n">
+        <v>46119.66666666666</v>
+      </c>
+      <c r="C1219" s="2" t="n">
+        <v>46119.67083333333</v>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>COQ-12</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>SISTEMA PITCH</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1220" s="2" t="n">
+        <v>46119.67361111111</v>
+      </c>
+      <c r="C1220" s="2" t="n">
+        <v>46119.67708333334</v>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>COQ-12</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>CONVERSOR</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1220" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1221" s="2" t="n">
+        <v>46119.67361111111</v>
+      </c>
+      <c r="C1221" s="2" t="n">
+        <v>46119.67708333334</v>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>COQ-12</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>GERADOR</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1222" s="2" t="n">
+        <v>46119.67361111111</v>
+      </c>
+      <c r="C1222" s="2" t="n">
+        <v>46119.6875</v>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>COQ-12</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>NACELLE</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1223" s="2" t="n">
+        <v>46119.68402777778</v>
+      </c>
+      <c r="C1223" s="2" t="n">
+        <v>46119.70069444444</v>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>COQ-12</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>TORRE WTG</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1224" s="2" t="n">
+        <v>46119.69930555556</v>
+      </c>
+      <c r="C1224" s="2" t="n">
+        <v>46119.70486111111</v>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>COQ-13</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>NACELLE</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>MPP1 - INSPEÇÃO EXTERNA DE AEROGERADOR - M6</t>
+        </is>
+      </c>
+      <c r="G1224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1225" s="2" t="n">
+        <v>46120.375</v>
+      </c>
+      <c r="C1225" s="2" t="n">
+        <v>46120.62569444445</v>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>MOR-18</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>NACELLE</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+        </is>
+      </c>
+      <c r="G1225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1226" s="2" t="n">
+        <v>46120.41666666666</v>
+      </c>
+      <c r="C1226" s="2" t="n">
+        <v>46120.66666666666</v>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>MOR-18</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>TORRE WTG</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+        </is>
+      </c>
+      <c r="G1226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1227" s="2" t="n">
+        <v>46120.45833333334</v>
+      </c>
+      <c r="C1227" s="2" t="n">
+        <v>46120.58333333334</v>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>MOR-18</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>GERADOR</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+        </is>
+      </c>
+      <c r="G1227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1228" s="2" t="n">
+        <v>46122.33333333334</v>
+      </c>
+      <c r="C1228" s="2" t="n">
         <v>46122.375</v>
       </c>
-      <c r="C1218" s="2" t="n">
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>COQ-17</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>GERADOR</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+        </is>
+      </c>
+      <c r="G1228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1229" s="2" t="n">
+        <v>46122.33333333334</v>
+      </c>
+      <c r="C1229" s="2" t="n">
+        <v>46122.41666666666</v>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>COQ-17</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>SISTEMA PITCH</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+        </is>
+      </c>
+      <c r="G1229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1230" s="2" t="n">
+        <v>46122.33333333334</v>
+      </c>
+      <c r="C1230" s="2" t="n">
+        <v>46122.5</v>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>COQ-17</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>NACELLE</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
+        </is>
+      </c>
+      <c r="G1230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="B1231" s="2" t="n">
+        <v>46122.375</v>
+      </c>
+      <c r="C1231" s="2" t="n">
         <v>46125.45833333334</v>
       </c>
-      <c r="D1218" t="inlineStr">
+      <c r="D1231" t="inlineStr">
         <is>
           <t>COQ-17</t>
         </is>
       </c>
-      <c r="E1218" t="inlineStr">
+      <c r="E1231" t="inlineStr">
         <is>
           <t>TORRE WTG</t>
         </is>
       </c>
-      <c r="F1218" t="inlineStr">
+      <c r="F1231" t="inlineStr">
         <is>
           <t>INSPEÇÃO DE MANUTENÇÃO PREVENTIVA ANUAL</t>
         </is>
       </c>
-      <c r="G1218" t="n">
+      <c r="G1231" t="n">
         <v>1</v>
       </c>
     </row>
